--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.23893460019962</v>
+        <v>4.913826872532439</v>
       </c>
       <c r="D2" t="n">
-        <v>30.53409412934747</v>
+        <v>4.961790296018964</v>
       </c>
       <c r="E2" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F2" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.76694960110472</v>
+        <v>4.349629310179517</v>
       </c>
       <c r="D3" t="n">
-        <v>27.07918593280304</v>
+        <v>4.400367714080494</v>
       </c>
       <c r="E3" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F3" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.74422928377806</v>
+        <v>10.03343725861393</v>
       </c>
       <c r="D4" t="n">
-        <v>58.07244997677643</v>
+        <v>9.436773121226169</v>
       </c>
       <c r="E4" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F4" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.39021725124294</v>
+        <v>9.650910303326979</v>
       </c>
       <c r="D5" t="n">
-        <v>55.15311111188592</v>
+        <v>8.962380555681463</v>
       </c>
       <c r="E5" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F5" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.24177212553164</v>
+        <v>2.964287970398891</v>
       </c>
       <c r="D6" t="n">
-        <v>17.84188898473961</v>
+        <v>2.899306960020187</v>
       </c>
       <c r="E6" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F6" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>64.2619481163381</v>
+        <v>10.44256656890494</v>
       </c>
       <c r="D7" t="n">
-        <v>59.23976128684089</v>
+        <v>9.626461209111644</v>
       </c>
       <c r="E7" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F7" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>60.5751737623077</v>
+        <v>9.843465736375002</v>
       </c>
       <c r="D8" t="n">
-        <v>55.69186017048681</v>
+        <v>9.049927277704105</v>
       </c>
       <c r="E8" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F8" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>68.8700551847143</v>
+        <v>11.19138396751607</v>
       </c>
       <c r="D9" t="n">
-        <v>63.75381672189273</v>
+        <v>10.35999521730757</v>
       </c>
       <c r="E9" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F9" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.87506074796208</v>
+        <v>6.967197371543838</v>
       </c>
       <c r="D10" t="n">
-        <v>37.88561006870847</v>
+        <v>6.156411636165127</v>
       </c>
       <c r="E10" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F10" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>51.66246930320877</v>
+        <v>8.395151261771426</v>
       </c>
       <c r="D11" t="n">
-        <v>46.5466381783858</v>
+        <v>7.563828703987692</v>
       </c>
       <c r="E11" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F11" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.58219586393359</v>
+        <v>4.319606827889208</v>
       </c>
       <c r="D12" t="n">
-        <v>24.21277407379624</v>
+        <v>3.93457578699189</v>
       </c>
       <c r="E12" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F12" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.73630269759395</v>
+        <v>4.182149188359016</v>
       </c>
       <c r="D13" t="n">
-        <v>28.9491652253589</v>
+        <v>4.704239349120821</v>
       </c>
       <c r="E13" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F13" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.48371375592313</v>
+        <v>7.066103485337508</v>
       </c>
       <c r="D14" t="n">
-        <v>38.63583276594602</v>
+        <v>6.278322824466229</v>
       </c>
       <c r="E14" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F14" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.6053447401247</v>
+        <v>5.785868520270264</v>
       </c>
       <c r="D15" t="n">
-        <v>40.64799800734149</v>
+        <v>6.605299676192992</v>
       </c>
       <c r="E15" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F15" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>13.21736732135392</v>
+        <v>2.147822189720011</v>
       </c>
       <c r="D16" t="n">
-        <v>8.105739311452053</v>
+        <v>1.317182638110959</v>
       </c>
       <c r="E16" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F16" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>22.24714783044903</v>
+        <v>3.615161522447967</v>
       </c>
       <c r="D17" t="n">
-        <v>18.93708505231728</v>
+        <v>3.077276321001559</v>
       </c>
       <c r="E17" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F17" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8.526126062222708</v>
+        <v>1.38549548511119</v>
       </c>
       <c r="D18" t="n">
-        <v>10.280312652888</v>
+        <v>1.6705508060943</v>
       </c>
       <c r="E18" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F18" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>15.84937064627803</v>
+        <v>2.57552273002018</v>
       </c>
       <c r="D19" t="n">
-        <v>19.99044910840064</v>
+        <v>3.248447980115103</v>
       </c>
       <c r="E19" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F19" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>16.67195066148681</v>
+        <v>2.709191982491607</v>
       </c>
       <c r="D20" t="n">
-        <v>5.935759614890997</v>
+        <v>0.964560937419787</v>
       </c>
       <c r="E20" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F20" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>31.92734599402559</v>
+        <v>5.188193724029158</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06771253646007</v>
+        <v>1.798503287174761</v>
       </c>
       <c r="E21" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F21" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>54.69410593612821</v>
+        <v>8.887792214620834</v>
       </c>
       <c r="D22" t="n">
-        <v>14.20244278960108</v>
+        <v>2.307896953310175</v>
       </c>
       <c r="E22" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F22" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>36.62493203337846</v>
+        <v>5.951551455424001</v>
       </c>
       <c r="D23" t="n">
-        <v>30.96563489428405</v>
+        <v>5.031915670321158</v>
       </c>
       <c r="E23" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F23" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>60.79427959241682</v>
+        <v>9.879070433767733</v>
       </c>
       <c r="D24" t="n">
-        <v>15.80922526293157</v>
+        <v>2.56899910522638</v>
       </c>
       <c r="E24" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F24" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>34.44631467819637</v>
+        <v>5.597526135206911</v>
       </c>
       <c r="D25" t="n">
-        <v>15.96754857442908</v>
+        <v>2.594726643344725</v>
       </c>
       <c r="E25" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F25" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>63.60154597757326</v>
+        <v>10.33525122135566</v>
       </c>
       <c r="D26" t="n">
-        <v>12.41038542010076</v>
+        <v>2.016687630766373</v>
       </c>
       <c r="E26" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F26" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>55.04733195674024</v>
+        <v>8.945191442970289</v>
       </c>
       <c r="D27" t="n">
-        <v>38.70177766102028</v>
+        <v>6.289038869915796</v>
       </c>
       <c r="E27" t="n">
-        <v>18.27450292840183</v>
+        <v>2.969606725865297</v>
       </c>
       <c r="F27" t="n">
-        <v>17.37681668957627</v>
+        <v>2.823732712056144</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
